--- a/aula03 excel/tabuada.xlsx
+++ b/aula03 excel/tabuada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\karlos henrique\aula03 excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A2208AE-DE25-4893-A1B7-D236C50A02A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBE1F91-8A7D-4C8E-A48F-68EC38B6A089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3C09E48F-3394-4EC0-950E-1E9F5C9C83FC}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="16035" windowHeight="11295" xr2:uid="{3C09E48F-3394-4EC0-950E-1E9F5C9C83FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -139,13 +139,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -156,11 +158,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,224 +491,213 @@
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>5</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <f>A2*B2</f>
         <v>5</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="7">
+      <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="2">
         <f>E2*F$1</f>
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <f t="shared" ref="C3:C11" si="0">A3*B3</f>
         <v>10</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7">
+      <c r="E3" s="2">
         <v>2</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F11" si="1">E3*F$1</f>
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
-        <v>5</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="B4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7">
+      <c r="E4" s="2">
         <v>3</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="2">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
-        <v>5</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="B5" s="2">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="7">
+      <c r="E5" s="2">
         <v>4</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="2">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>5</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="7">
-        <v>5</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="7">
+      <c r="E7" s="2">
         <v>6</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="2">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="7">
+      <c r="E8" s="2">
         <v>7</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="2">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="7">
+      <c r="E9" s="2">
         <v>8</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="2">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="7">
-        <v>5</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="7">
+      <c r="E10" s="2">
         <v>9</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="2">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="7">
-        <v>5</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="2">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="7">
+      <c r="E11" s="2">
         <v>10</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="2">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="E12" s="1" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="E12" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
